--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125699588</v>
+        <v>125699592</v>
       </c>
       <c r="B15" t="n">
-        <v>91392</v>
+        <v>56843</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1588</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789477</v>
+        <v>789386</v>
       </c>
       <c r="R15" t="n">
-        <v>7358460</v>
+        <v>7358462</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2023,6 +2023,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2049,7 +2054,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699587</v>
+        <v>125699588</v>
       </c>
       <c r="B16" t="n">
         <v>91392</v>
@@ -2084,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789479</v>
+        <v>789477</v>
       </c>
       <c r="R16" t="n">
-        <v>7358457</v>
+        <v>7358460</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2146,32 +2151,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699592</v>
+        <v>125699587</v>
       </c>
       <c r="B17" t="n">
-        <v>56843</v>
+        <v>91392</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1588</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2186,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789386</v>
+        <v>789479</v>
       </c>
       <c r="R17" t="n">
-        <v>7358462</v>
+        <v>7358457</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2217,11 +2222,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2248,32 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699593</v>
+        <v>125699597</v>
       </c>
       <c r="B18" t="n">
-        <v>56843</v>
+        <v>57811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789386</v>
+        <v>789475</v>
       </c>
       <c r="R18" t="n">
-        <v>7358451</v>
+        <v>7358466</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,11 +2319,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2350,32 +2345,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125699597</v>
+        <v>125699593</v>
       </c>
       <c r="B19" t="n">
-        <v>57811</v>
+        <v>56843</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2385,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789475</v>
+        <v>789386</v>
       </c>
       <c r="R19" t="n">
-        <v>7358466</v>
+        <v>7358451</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2421,6 +2416,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125699614</v>
       </c>
       <c r="B2" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>125699611</v>
       </c>
       <c r="B3" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>125699612</v>
       </c>
       <c r="B5" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>125699610</v>
       </c>
       <c r="B6" t="n">
-        <v>97208</v>
+        <v>97215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>125699615</v>
       </c>
       <c r="B8" t="n">
-        <v>92496</v>
+        <v>92503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125699608</v>
       </c>
       <c r="B11" t="n">
-        <v>97208</v>
+        <v>97215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>125699609</v>
       </c>
       <c r="B14" t="n">
-        <v>97208</v>
+        <v>97215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125699592</v>
+        <v>125699588</v>
       </c>
       <c r="B15" t="n">
-        <v>56843</v>
+        <v>91399</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>1588</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789386</v>
+        <v>789477</v>
       </c>
       <c r="R15" t="n">
-        <v>7358462</v>
+        <v>7358460</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2023,11 +2023,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2054,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699588</v>
+        <v>125699587</v>
       </c>
       <c r="B16" t="n">
-        <v>91392</v>
+        <v>91399</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789477</v>
+        <v>789479</v>
       </c>
       <c r="R16" t="n">
-        <v>7358460</v>
+        <v>7358457</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2151,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699587</v>
+        <v>125699592</v>
       </c>
       <c r="B17" t="n">
-        <v>91392</v>
+        <v>56843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1588</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2186,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789479</v>
+        <v>789386</v>
       </c>
       <c r="R17" t="n">
-        <v>7358457</v>
+        <v>7358462</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2222,6 +2217,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2248,32 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699597</v>
+        <v>125699593</v>
       </c>
       <c r="B18" t="n">
-        <v>57811</v>
+        <v>56843</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789475</v>
+        <v>789386</v>
       </c>
       <c r="R18" t="n">
-        <v>7358466</v>
+        <v>7358451</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,6 +2319,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2345,32 +2350,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125699593</v>
+        <v>125699597</v>
       </c>
       <c r="B19" t="n">
-        <v>56843</v>
+        <v>57811</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2385,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789386</v>
+        <v>789475</v>
       </c>
       <c r="R19" t="n">
-        <v>7358451</v>
+        <v>7358466</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2416,11 +2421,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699612</v>
+        <v>125699610</v>
       </c>
       <c r="B5" t="n">
-        <v>96457</v>
+        <v>97215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789550</v>
+        <v>789467</v>
       </c>
       <c r="R5" t="n">
-        <v>7358395</v>
+        <v>7358419</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699610</v>
+        <v>125699612</v>
       </c>
       <c r="B6" t="n">
-        <v>97215</v>
+        <v>96457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789467</v>
+        <v>789550</v>
       </c>
       <c r="R6" t="n">
-        <v>7358419</v>
+        <v>7358395</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -1758,32 +1758,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125699589</v>
+        <v>125699609</v>
       </c>
       <c r="B13" t="n">
-        <v>79585</v>
+        <v>97215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789400</v>
+        <v>789218</v>
       </c>
       <c r="R13" t="n">
-        <v>7358476</v>
+        <v>7358692</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125699609</v>
+        <v>125699589</v>
       </c>
       <c r="B14" t="n">
-        <v>97215</v>
+        <v>79585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789218</v>
+        <v>789400</v>
       </c>
       <c r="R14" t="n">
-        <v>7358692</v>
+        <v>7358476</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2248,32 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699593</v>
+        <v>125699597</v>
       </c>
       <c r="B18" t="n">
-        <v>56843</v>
+        <v>57811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789386</v>
+        <v>789475</v>
       </c>
       <c r="R18" t="n">
-        <v>7358451</v>
+        <v>7358466</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,11 +2319,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2350,32 +2345,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125699597</v>
+        <v>125699593</v>
       </c>
       <c r="B19" t="n">
-        <v>57811</v>
+        <v>56843</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2385,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789475</v>
+        <v>789386</v>
       </c>
       <c r="R19" t="n">
-        <v>7358466</v>
+        <v>7358451</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2421,6 +2416,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125699614</v>
       </c>
       <c r="B2" t="n">
-        <v>96457</v>
+        <v>96460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>125699611</v>
       </c>
       <c r="B3" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699610</v>
+        <v>125699612</v>
       </c>
       <c r="B5" t="n">
-        <v>97215</v>
+        <v>96460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789467</v>
+        <v>789550</v>
       </c>
       <c r="R5" t="n">
-        <v>7358419</v>
+        <v>7358395</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699612</v>
+        <v>125699610</v>
       </c>
       <c r="B6" t="n">
-        <v>96457</v>
+        <v>97218</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789550</v>
+        <v>789467</v>
       </c>
       <c r="R6" t="n">
-        <v>7358395</v>
+        <v>7358419</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1266,7 +1266,7 @@
         <v>125699615</v>
       </c>
       <c r="B8" t="n">
-        <v>92503</v>
+        <v>92512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>125699590</v>
       </c>
       <c r="B10" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125699608</v>
       </c>
       <c r="B11" t="n">
-        <v>97215</v>
+        <v>97218</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>125699591</v>
       </c>
       <c r="B12" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>125699609</v>
       </c>
       <c r="B13" t="n">
-        <v>97215</v>
+        <v>97218</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>125699589</v>
       </c>
       <c r="B14" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125699588</v>
+        <v>125699587</v>
       </c>
       <c r="B15" t="n">
-        <v>91399</v>
+        <v>91403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789477</v>
+        <v>789479</v>
       </c>
       <c r="R15" t="n">
-        <v>7358460</v>
+        <v>7358457</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699587</v>
+        <v>125699588</v>
       </c>
       <c r="B16" t="n">
-        <v>91399</v>
+        <v>91403</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789479</v>
+        <v>789477</v>
       </c>
       <c r="R16" t="n">
-        <v>7358457</v>
+        <v>7358460</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2248,32 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699597</v>
+        <v>125699593</v>
       </c>
       <c r="B18" t="n">
-        <v>57811</v>
+        <v>56843</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789475</v>
+        <v>789386</v>
       </c>
       <c r="R18" t="n">
-        <v>7358466</v>
+        <v>7358451</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,6 +2319,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2345,32 +2350,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125699593</v>
+        <v>125699597</v>
       </c>
       <c r="B19" t="n">
-        <v>56843</v>
+        <v>57811</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2385,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789386</v>
+        <v>789475</v>
       </c>
       <c r="R19" t="n">
-        <v>7358451</v>
+        <v>7358466</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2416,11 +2421,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125699608</v>
+        <v>125699591</v>
       </c>
       <c r="B11" t="n">
-        <v>97218</v>
+        <v>79557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789136</v>
+        <v>789411</v>
       </c>
       <c r="R11" t="n">
-        <v>7358773</v>
+        <v>7358493</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1642,6 +1642,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1660,32 +1661,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125699591</v>
+        <v>125699608</v>
       </c>
       <c r="B12" t="n">
-        <v>79557</v>
+        <v>97218</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789411</v>
+        <v>789136</v>
       </c>
       <c r="R12" t="n">
-        <v>7358493</v>
+        <v>7358773</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1739,7 +1740,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125699614</v>
       </c>
       <c r="B2" t="n">
-        <v>96460</v>
+        <v>96464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125699611</v>
+        <v>125699595</v>
       </c>
       <c r="B3" t="n">
-        <v>92518</v>
+        <v>56843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>789445</v>
+        <v>789400</v>
       </c>
       <c r="R3" t="n">
-        <v>7358421</v>
+        <v>7358442</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125699595</v>
+        <v>125699611</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>92522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789400</v>
+        <v>789445</v>
       </c>
       <c r="R4" t="n">
-        <v>7358442</v>
+        <v>7358421</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699612</v>
+        <v>125699610</v>
       </c>
       <c r="B5" t="n">
-        <v>96460</v>
+        <v>97222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789550</v>
+        <v>789467</v>
       </c>
       <c r="R5" t="n">
-        <v>7358395</v>
+        <v>7358419</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699610</v>
+        <v>125699612</v>
       </c>
       <c r="B6" t="n">
-        <v>97218</v>
+        <v>96464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789467</v>
+        <v>789550</v>
       </c>
       <c r="R6" t="n">
-        <v>7358419</v>
+        <v>7358395</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1266,7 +1266,7 @@
         <v>125699615</v>
       </c>
       <c r="B8" t="n">
-        <v>92512</v>
+        <v>92516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>125699590</v>
       </c>
       <c r="B10" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125699591</v>
+        <v>125699608</v>
       </c>
       <c r="B11" t="n">
-        <v>79557</v>
+        <v>97222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789411</v>
+        <v>789136</v>
       </c>
       <c r="R11" t="n">
-        <v>7358493</v>
+        <v>7358773</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1642,7 +1642,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1661,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125699608</v>
+        <v>125699591</v>
       </c>
       <c r="B12" t="n">
-        <v>97218</v>
+        <v>79561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789136</v>
+        <v>789411</v>
       </c>
       <c r="R12" t="n">
-        <v>7358773</v>
+        <v>7358493</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1740,6 +1739,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>125699609</v>
       </c>
       <c r="B13" t="n">
-        <v>97218</v>
+        <v>97222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>125699589</v>
       </c>
       <c r="B14" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125699587</v>
+        <v>125699588</v>
       </c>
       <c r="B15" t="n">
-        <v>91403</v>
+        <v>91407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789479</v>
+        <v>789477</v>
       </c>
       <c r="R15" t="n">
-        <v>7358457</v>
+        <v>7358460</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699588</v>
+        <v>125699587</v>
       </c>
       <c r="B16" t="n">
-        <v>91403</v>
+        <v>91407</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789477</v>
+        <v>789479</v>
       </c>
       <c r="R16" t="n">
-        <v>7358460</v>
+        <v>7358457</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -773,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125699595</v>
+        <v>125699611</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>92522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>789400</v>
+        <v>789445</v>
       </c>
       <c r="R3" t="n">
-        <v>7358442</v>
+        <v>7358421</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125699611</v>
+        <v>125699595</v>
       </c>
       <c r="B4" t="n">
-        <v>92522</v>
+        <v>56843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789445</v>
+        <v>789400</v>
       </c>
       <c r="R4" t="n">
-        <v>7358421</v>
+        <v>7358442</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699610</v>
+        <v>125699612</v>
       </c>
       <c r="B5" t="n">
-        <v>97222</v>
+        <v>96464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789467</v>
+        <v>789550</v>
       </c>
       <c r="R5" t="n">
-        <v>7358419</v>
+        <v>7358395</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699612</v>
+        <v>125699610</v>
       </c>
       <c r="B6" t="n">
-        <v>96464</v>
+        <v>97222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789550</v>
+        <v>789467</v>
       </c>
       <c r="R6" t="n">
-        <v>7358395</v>
+        <v>7358419</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125699614</v>
       </c>
       <c r="B2" t="n">
-        <v>96464</v>
+        <v>96465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699612</v>
+        <v>125699610</v>
       </c>
       <c r="B5" t="n">
-        <v>96464</v>
+        <v>97223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789550</v>
+        <v>789467</v>
       </c>
       <c r="R5" t="n">
-        <v>7358395</v>
+        <v>7358419</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699610</v>
+        <v>125699612</v>
       </c>
       <c r="B6" t="n">
-        <v>97222</v>
+        <v>96465</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789467</v>
+        <v>789550</v>
       </c>
       <c r="R6" t="n">
-        <v>7358419</v>
+        <v>7358395</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1566,7 +1566,7 @@
         <v>125699608</v>
       </c>
       <c r="B11" t="n">
-        <v>97222</v>
+        <v>97223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>125699609</v>
       </c>
       <c r="B13" t="n">
-        <v>97222</v>
+        <v>97223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2248,32 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699593</v>
+        <v>125699597</v>
       </c>
       <c r="B18" t="n">
-        <v>56843</v>
+        <v>57811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789386</v>
+        <v>789475</v>
       </c>
       <c r="R18" t="n">
-        <v>7358451</v>
+        <v>7358466</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,11 +2319,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2350,32 +2345,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125699597</v>
+        <v>125699593</v>
       </c>
       <c r="B19" t="n">
-        <v>57811</v>
+        <v>56843</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2385,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789475</v>
+        <v>789386</v>
       </c>
       <c r="R19" t="n">
-        <v>7358466</v>
+        <v>7358451</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2421,6 +2416,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -773,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125699611</v>
+        <v>125699595</v>
       </c>
       <c r="B3" t="n">
-        <v>92522</v>
+        <v>56843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>789445</v>
+        <v>789400</v>
       </c>
       <c r="R3" t="n">
-        <v>7358421</v>
+        <v>7358442</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125699595</v>
+        <v>125699611</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>92522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789400</v>
+        <v>789445</v>
       </c>
       <c r="R4" t="n">
-        <v>7358442</v>
+        <v>7358421</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699610</v>
+        <v>125699612</v>
       </c>
       <c r="B5" t="n">
-        <v>97223</v>
+        <v>96465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789467</v>
+        <v>789550</v>
       </c>
       <c r="R5" t="n">
-        <v>7358419</v>
+        <v>7358395</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699612</v>
+        <v>125699610</v>
       </c>
       <c r="B6" t="n">
-        <v>96465</v>
+        <v>97223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789550</v>
+        <v>789467</v>
       </c>
       <c r="R6" t="n">
-        <v>7358395</v>
+        <v>7358419</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1758,32 +1758,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125699609</v>
+        <v>125699589</v>
       </c>
       <c r="B13" t="n">
-        <v>97223</v>
+        <v>79590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789218</v>
+        <v>789400</v>
       </c>
       <c r="R13" t="n">
-        <v>7358692</v>
+        <v>7358476</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125699589</v>
+        <v>125699609</v>
       </c>
       <c r="B14" t="n">
-        <v>79590</v>
+        <v>97223</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789400</v>
+        <v>789218</v>
       </c>
       <c r="R14" t="n">
-        <v>7358476</v>
+        <v>7358692</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125699614</v>
       </c>
       <c r="B2" t="n">
-        <v>96465</v>
+        <v>96467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125699595</v>
+        <v>125699611</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>92524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>789400</v>
+        <v>789445</v>
       </c>
       <c r="R3" t="n">
-        <v>7358442</v>
+        <v>7358421</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125699611</v>
+        <v>125699595</v>
       </c>
       <c r="B4" t="n">
-        <v>92522</v>
+        <v>56844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789445</v>
+        <v>789400</v>
       </c>
       <c r="R4" t="n">
-        <v>7358421</v>
+        <v>7358442</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -970,7 +970,7 @@
         <v>125699612</v>
       </c>
       <c r="B5" t="n">
-        <v>96465</v>
+        <v>96467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>125699610</v>
       </c>
       <c r="B6" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>125699594</v>
       </c>
       <c r="B7" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,45 +1263,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125699615</v>
+        <v>125699596</v>
       </c>
       <c r="B8" t="n">
-        <v>92516</v>
+        <v>56844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill Hällforsen, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789412</v>
+        <v>789460</v>
       </c>
       <c r="R8" t="n">
-        <v>7358452</v>
+        <v>7358448</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1334,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1360,49 +1369,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125699596</v>
+        <v>125699615</v>
       </c>
       <c r="B9" t="n">
-        <v>56843</v>
+        <v>92518</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill Hällforsen, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789460</v>
+        <v>789412</v>
       </c>
       <c r="R9" t="n">
-        <v>7358448</v>
+        <v>7358452</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1435,11 +1440,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1469,7 @@
         <v>125699590</v>
       </c>
       <c r="B10" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125699608</v>
       </c>
       <c r="B11" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>125699591</v>
       </c>
       <c r="B12" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,32 +1758,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125699589</v>
+        <v>125699609</v>
       </c>
       <c r="B13" t="n">
-        <v>79590</v>
+        <v>97225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789400</v>
+        <v>789218</v>
       </c>
       <c r="R13" t="n">
-        <v>7358476</v>
+        <v>7358692</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125699609</v>
+        <v>125699589</v>
       </c>
       <c r="B14" t="n">
-        <v>97223</v>
+        <v>79591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789218</v>
+        <v>789400</v>
       </c>
       <c r="R14" t="n">
-        <v>7358692</v>
+        <v>7358476</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125699588</v>
+        <v>125699587</v>
       </c>
       <c r="B15" t="n">
-        <v>91407</v>
+        <v>91409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789477</v>
+        <v>789479</v>
       </c>
       <c r="R15" t="n">
-        <v>7358460</v>
+        <v>7358457</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699587</v>
+        <v>125699588</v>
       </c>
       <c r="B16" t="n">
-        <v>91407</v>
+        <v>91409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789479</v>
+        <v>789477</v>
       </c>
       <c r="R16" t="n">
-        <v>7358457</v>
+        <v>7358460</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2149,7 +2149,7 @@
         <v>125699592</v>
       </c>
       <c r="B17" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>125699597</v>
       </c>
       <c r="B18" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>125699593</v>
       </c>
       <c r="B19" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125699587</v>
+        <v>125699592</v>
       </c>
       <c r="B15" t="n">
-        <v>91409</v>
+        <v>56844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1588</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789479</v>
+        <v>789386</v>
       </c>
       <c r="R15" t="n">
-        <v>7358457</v>
+        <v>7358462</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2023,6 +2023,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2049,7 +2054,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699588</v>
+        <v>125699587</v>
       </c>
       <c r="B16" t="n">
         <v>91409</v>
@@ -2084,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789477</v>
+        <v>789479</v>
       </c>
       <c r="R16" t="n">
-        <v>7358460</v>
+        <v>7358457</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2146,32 +2151,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699592</v>
+        <v>125699588</v>
       </c>
       <c r="B17" t="n">
-        <v>56844</v>
+        <v>91409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1588</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2186,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789386</v>
+        <v>789477</v>
       </c>
       <c r="R17" t="n">
-        <v>7358462</v>
+        <v>7358460</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2217,11 +2222,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125699614</v>
       </c>
       <c r="B2" t="n">
-        <v>96467</v>
+        <v>96469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>125699611</v>
       </c>
       <c r="B3" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>125699612</v>
       </c>
       <c r="B5" t="n">
-        <v>96467</v>
+        <v>96469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>125699610</v>
       </c>
       <c r="B6" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>125699615</v>
       </c>
       <c r="B9" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125699608</v>
+        <v>125699591</v>
       </c>
       <c r="B11" t="n">
-        <v>97225</v>
+        <v>79562</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789136</v>
+        <v>789411</v>
       </c>
       <c r="R11" t="n">
-        <v>7358773</v>
+        <v>7358493</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1642,6 +1642,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1660,32 +1661,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125699591</v>
+        <v>125699608</v>
       </c>
       <c r="B12" t="n">
-        <v>79562</v>
+        <v>97227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789411</v>
+        <v>789136</v>
       </c>
       <c r="R12" t="n">
-        <v>7358493</v>
+        <v>7358773</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1739,7 +1740,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>125699609</v>
       </c>
       <c r="B13" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125699592</v>
+        <v>125699588</v>
       </c>
       <c r="B15" t="n">
-        <v>56844</v>
+        <v>91411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>1588</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789386</v>
+        <v>789477</v>
       </c>
       <c r="R15" t="n">
-        <v>7358462</v>
+        <v>7358460</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2023,11 +2023,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2057,7 +2052,7 @@
         <v>125699587</v>
       </c>
       <c r="B16" t="n">
-        <v>91409</v>
+        <v>91411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699588</v>
+        <v>125699592</v>
       </c>
       <c r="B17" t="n">
-        <v>91409</v>
+        <v>56844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1588</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2186,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789477</v>
+        <v>789386</v>
       </c>
       <c r="R17" t="n">
-        <v>7358460</v>
+        <v>7358462</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2222,6 +2217,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2248,32 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699597</v>
+        <v>125699593</v>
       </c>
       <c r="B18" t="n">
-        <v>57812</v>
+        <v>56844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789475</v>
+        <v>789386</v>
       </c>
       <c r="R18" t="n">
-        <v>7358466</v>
+        <v>7358451</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,6 +2319,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2345,32 +2350,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125699593</v>
+        <v>125699597</v>
       </c>
       <c r="B19" t="n">
-        <v>56844</v>
+        <v>57812</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2385,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789386</v>
+        <v>789475</v>
       </c>
       <c r="R19" t="n">
-        <v>7358451</v>
+        <v>7358466</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2416,11 +2421,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -1263,49 +1263,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125699596</v>
+        <v>125699615</v>
       </c>
       <c r="B8" t="n">
-        <v>56844</v>
+        <v>92520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill Hällforsen, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789460</v>
+        <v>789412</v>
       </c>
       <c r="R8" t="n">
-        <v>7358448</v>
+        <v>7358452</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1338,11 +1334,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,45 +1360,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125699615</v>
+        <v>125699596</v>
       </c>
       <c r="B9" t="n">
-        <v>92520</v>
+        <v>56844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill Hällforsen, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789412</v>
+        <v>789460</v>
       </c>
       <c r="R9" t="n">
-        <v>7358452</v>
+        <v>7358448</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1440,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125699614</v>
       </c>
       <c r="B2" t="n">
-        <v>96469</v>
+        <v>96471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125699611</v>
+        <v>125699595</v>
       </c>
       <c r="B3" t="n">
-        <v>92526</v>
+        <v>56844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>789445</v>
+        <v>789400</v>
       </c>
       <c r="R3" t="n">
-        <v>7358421</v>
+        <v>7358442</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125699595</v>
+        <v>125699611</v>
       </c>
       <c r="B4" t="n">
-        <v>56844</v>
+        <v>92528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789400</v>
+        <v>789445</v>
       </c>
       <c r="R4" t="n">
-        <v>7358442</v>
+        <v>7358421</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -970,7 +970,7 @@
         <v>125699612</v>
       </c>
       <c r="B5" t="n">
-        <v>96469</v>
+        <v>96471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>125699610</v>
       </c>
       <c r="B6" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>125699615</v>
       </c>
       <c r="B8" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125699591</v>
+        <v>125699608</v>
       </c>
       <c r="B11" t="n">
-        <v>79562</v>
+        <v>97229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789411</v>
+        <v>789136</v>
       </c>
       <c r="R11" t="n">
-        <v>7358493</v>
+        <v>7358773</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1642,7 +1642,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1661,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125699608</v>
+        <v>125699591</v>
       </c>
       <c r="B12" t="n">
-        <v>97227</v>
+        <v>79562</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789136</v>
+        <v>789411</v>
       </c>
       <c r="R12" t="n">
-        <v>7358773</v>
+        <v>7358493</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1740,6 +1739,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1758,32 +1758,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125699609</v>
+        <v>125699589</v>
       </c>
       <c r="B13" t="n">
-        <v>97227</v>
+        <v>79591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789218</v>
+        <v>789400</v>
       </c>
       <c r="R13" t="n">
-        <v>7358692</v>
+        <v>7358476</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125699589</v>
+        <v>125699609</v>
       </c>
       <c r="B14" t="n">
-        <v>79591</v>
+        <v>97229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789400</v>
+        <v>789218</v>
       </c>
       <c r="R14" t="n">
-        <v>7358476</v>
+        <v>7358692</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1955,7 +1955,7 @@
         <v>125699588</v>
       </c>
       <c r="B15" t="n">
-        <v>91411</v>
+        <v>91413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>125699587</v>
       </c>
       <c r="B16" t="n">
-        <v>91411</v>
+        <v>91413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,32 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699593</v>
+        <v>125699597</v>
       </c>
       <c r="B18" t="n">
-        <v>56844</v>
+        <v>57812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789386</v>
+        <v>789475</v>
       </c>
       <c r="R18" t="n">
-        <v>7358451</v>
+        <v>7358466</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,11 +2319,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2350,32 +2345,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125699597</v>
+        <v>125699593</v>
       </c>
       <c r="B19" t="n">
-        <v>57812</v>
+        <v>56844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2385,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789475</v>
+        <v>789386</v>
       </c>
       <c r="R19" t="n">
-        <v>7358466</v>
+        <v>7358451</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2421,6 +2416,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -773,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125699595</v>
+        <v>125699611</v>
       </c>
       <c r="B3" t="n">
-        <v>56844</v>
+        <v>92528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>789400</v>
+        <v>789445</v>
       </c>
       <c r="R3" t="n">
-        <v>7358442</v>
+        <v>7358421</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125699611</v>
+        <v>125699595</v>
       </c>
       <c r="B4" t="n">
-        <v>92528</v>
+        <v>56844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789445</v>
+        <v>789400</v>
       </c>
       <c r="R4" t="n">
-        <v>7358421</v>
+        <v>7358442</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125699614</v>
       </c>
       <c r="B2" t="n">
-        <v>96471</v>
+        <v>96475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125699611</v>
+        <v>125699595</v>
       </c>
       <c r="B3" t="n">
-        <v>92528</v>
+        <v>56848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>789445</v>
+        <v>789400</v>
       </c>
       <c r="R3" t="n">
-        <v>7358421</v>
+        <v>7358442</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125699595</v>
+        <v>125699611</v>
       </c>
       <c r="B4" t="n">
-        <v>56844</v>
+        <v>92532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789400</v>
+        <v>789445</v>
       </c>
       <c r="R4" t="n">
-        <v>7358442</v>
+        <v>7358421</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699612</v>
+        <v>125699610</v>
       </c>
       <c r="B5" t="n">
-        <v>96471</v>
+        <v>97233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789550</v>
+        <v>789467</v>
       </c>
       <c r="R5" t="n">
-        <v>7358395</v>
+        <v>7358419</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699610</v>
+        <v>125699612</v>
       </c>
       <c r="B6" t="n">
-        <v>97229</v>
+        <v>96475</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789467</v>
+        <v>789550</v>
       </c>
       <c r="R6" t="n">
-        <v>7358419</v>
+        <v>7358395</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1164,7 +1164,7 @@
         <v>125699594</v>
       </c>
       <c r="B7" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>125699615</v>
       </c>
       <c r="B8" t="n">
-        <v>92522</v>
+        <v>92526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>125699596</v>
       </c>
       <c r="B9" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>125699590</v>
       </c>
       <c r="B10" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>125699608</v>
       </c>
       <c r="B11" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>125699591</v>
       </c>
       <c r="B12" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>125699589</v>
       </c>
       <c r="B13" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>125699609</v>
       </c>
       <c r="B14" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>125699588</v>
       </c>
       <c r="B15" t="n">
-        <v>91413</v>
+        <v>91417</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>125699587</v>
       </c>
       <c r="B16" t="n">
-        <v>91413</v>
+        <v>91417</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>125699592</v>
       </c>
       <c r="B17" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>125699597</v>
       </c>
       <c r="B18" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>125699593</v>
       </c>
       <c r="B19" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -1758,32 +1758,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125699589</v>
+        <v>125699609</v>
       </c>
       <c r="B13" t="n">
-        <v>79595</v>
+        <v>97233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789400</v>
+        <v>789218</v>
       </c>
       <c r="R13" t="n">
-        <v>7358476</v>
+        <v>7358692</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125699609</v>
+        <v>125699589</v>
       </c>
       <c r="B14" t="n">
-        <v>97233</v>
+        <v>79595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789218</v>
+        <v>789400</v>
       </c>
       <c r="R14" t="n">
-        <v>7358692</v>
+        <v>7358476</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125699614</v>
       </c>
       <c r="B2" t="n">
-        <v>96475</v>
+        <v>96478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699610</v>
+        <v>125699612</v>
       </c>
       <c r="B5" t="n">
-        <v>97233</v>
+        <v>96478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789467</v>
+        <v>789550</v>
       </c>
       <c r="R5" t="n">
-        <v>7358419</v>
+        <v>7358395</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699612</v>
+        <v>125699610</v>
       </c>
       <c r="B6" t="n">
-        <v>96475</v>
+        <v>97236</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789550</v>
+        <v>789467</v>
       </c>
       <c r="R6" t="n">
-        <v>7358395</v>
+        <v>7358419</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1263,45 +1263,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125699615</v>
+        <v>125699596</v>
       </c>
       <c r="B8" t="n">
-        <v>92526</v>
+        <v>56848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill Hällforsen, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789412</v>
+        <v>789460</v>
       </c>
       <c r="R8" t="n">
-        <v>7358452</v>
+        <v>7358448</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1334,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1360,49 +1369,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125699596</v>
+        <v>125699615</v>
       </c>
       <c r="B9" t="n">
-        <v>56848</v>
+        <v>92526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill Hällforsen, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789460</v>
+        <v>789412</v>
       </c>
       <c r="R9" t="n">
-        <v>7358448</v>
+        <v>7358452</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1435,11 +1440,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,7 +1566,7 @@
         <v>125699608</v>
       </c>
       <c r="B11" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>125699609</v>
       </c>
       <c r="B13" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125699588</v>
+        <v>125699587</v>
       </c>
       <c r="B15" t="n">
         <v>91417</v>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789477</v>
+        <v>789479</v>
       </c>
       <c r="R15" t="n">
-        <v>7358460</v>
+        <v>7358457</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2049,7 +2049,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699587</v>
+        <v>125699588</v>
       </c>
       <c r="B16" t="n">
         <v>91417</v>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789479</v>
+        <v>789477</v>
       </c>
       <c r="R16" t="n">
-        <v>7358457</v>
+        <v>7358460</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2248,32 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699597</v>
+        <v>125699593</v>
       </c>
       <c r="B18" t="n">
-        <v>57816</v>
+        <v>56848</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789475</v>
+        <v>789386</v>
       </c>
       <c r="R18" t="n">
-        <v>7358466</v>
+        <v>7358451</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,6 +2319,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2345,32 +2350,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125699593</v>
+        <v>125699597</v>
       </c>
       <c r="B19" t="n">
-        <v>56848</v>
+        <v>57816</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2385,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789386</v>
+        <v>789475</v>
       </c>
       <c r="R19" t="n">
-        <v>7358451</v>
+        <v>7358466</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2416,11 +2421,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
         <v>125699595</v>
       </c>
       <c r="B3" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>125699594</v>
       </c>
       <c r="B7" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>125699596</v>
       </c>
       <c r="B8" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>125699592</v>
       </c>
       <c r="B17" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>125699593</v>
       </c>
       <c r="B18" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
         <v>125699595</v>
       </c>
       <c r="B3" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>125699594</v>
       </c>
       <c r="B7" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>125699596</v>
       </c>
       <c r="B8" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>125699592</v>
       </c>
       <c r="B17" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>125699593</v>
       </c>
       <c r="B18" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
         <v>125699595</v>
       </c>
       <c r="B3" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>125699594</v>
       </c>
       <c r="B7" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>125699596</v>
       </c>
       <c r="B8" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>125699592</v>
       </c>
       <c r="B17" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>125699593</v>
       </c>
       <c r="B18" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -776,7 +776,7 @@
         <v>125699595</v>
       </c>
       <c r="B3" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>125699594</v>
       </c>
       <c r="B7" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>125699596</v>
       </c>
       <c r="B8" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>125699592</v>
       </c>
       <c r="B17" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>125699593</v>
       </c>
       <c r="B18" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125699614</v>
+        <v>125699587</v>
       </c>
       <c r="B2" t="n">
-        <v>96478</v>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>789549</v>
+        <v>789479</v>
       </c>
       <c r="R2" t="n">
-        <v>7358401</v>
+        <v>7358457</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -773,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125699595</v>
+        <v>125699588</v>
       </c>
       <c r="B3" t="n">
-        <v>57053</v>
+        <v>92097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1588</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -808,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>789400</v>
+        <v>789477</v>
       </c>
       <c r="R3" t="n">
-        <v>7358442</v>
+        <v>7358460</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125699611</v>
+        <v>125699612</v>
       </c>
       <c r="B4" t="n">
-        <v>92532</v>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789445</v>
+        <v>789550</v>
       </c>
       <c r="R4" t="n">
-        <v>7358421</v>
+        <v>7358395</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699612</v>
+        <v>125699614</v>
       </c>
       <c r="B5" t="n">
-        <v>96478</v>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789550</v>
+        <v>789549</v>
       </c>
       <c r="R5" t="n">
-        <v>7358395</v>
+        <v>7358401</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1046,6 +1045,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1064,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699610</v>
+        <v>125699615</v>
       </c>
       <c r="B6" t="n">
-        <v>97236</v>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789467</v>
+        <v>789412</v>
       </c>
       <c r="R6" t="n">
-        <v>7358419</v>
+        <v>7358452</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1161,32 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125699594</v>
+        <v>125699611</v>
       </c>
       <c r="B7" t="n">
-        <v>57053</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>789402</v>
+        <v>789445</v>
       </c>
       <c r="R7" t="n">
-        <v>7358474</v>
+        <v>7358421</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1232,11 +1232,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1263,49 +1258,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125699596</v>
+        <v>125699589</v>
       </c>
       <c r="B8" t="n">
-        <v>57053</v>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill Hällforsen, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789460</v>
+        <v>789400</v>
       </c>
       <c r="R8" t="n">
-        <v>7358448</v>
+        <v>7358476</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1338,11 +1329,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,10 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125699615</v>
+        <v>125699590</v>
       </c>
       <c r="B9" t="n">
-        <v>92526</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789412</v>
+        <v>789403</v>
       </c>
       <c r="R9" t="n">
-        <v>7358452</v>
+        <v>7358467</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1466,32 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125699590</v>
+        <v>125699592</v>
       </c>
       <c r="B10" t="n">
-        <v>79595</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789403</v>
+        <v>789386</v>
       </c>
       <c r="R10" t="n">
-        <v>7358467</v>
+        <v>7358462</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1537,6 +1523,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125699608</v>
+        <v>125699593</v>
       </c>
       <c r="B11" t="n">
-        <v>97236</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1565,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789136</v>
+        <v>789386</v>
       </c>
       <c r="R11" t="n">
-        <v>7358773</v>
+        <v>7358451</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1634,6 +1625,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,32 +1656,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125699591</v>
+        <v>125699594</v>
       </c>
       <c r="B12" t="n">
-        <v>79566</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789411</v>
+        <v>789402</v>
       </c>
       <c r="R12" t="n">
-        <v>7358493</v>
+        <v>7358474</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1733,13 +1729,17 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125699609</v>
+        <v>125699595</v>
       </c>
       <c r="B13" t="n">
-        <v>97236</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789218</v>
+        <v>789400</v>
       </c>
       <c r="R13" t="n">
-        <v>7358692</v>
+        <v>7358442</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1855,45 +1855,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125699589</v>
+        <v>125699596</v>
       </c>
       <c r="B14" t="n">
-        <v>79595</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lill Hällforsen, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789400</v>
+        <v>789460</v>
       </c>
       <c r="R14" t="n">
-        <v>7358476</v>
+        <v>7358448</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1926,6 +1930,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1952,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125699587</v>
+        <v>125699597</v>
       </c>
       <c r="B15" t="n">
-        <v>91417</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1972,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1588</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789479</v>
+        <v>789475</v>
       </c>
       <c r="R15" t="n">
-        <v>7358457</v>
+        <v>7358466</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2049,32 +2058,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699588</v>
+        <v>125699608</v>
       </c>
       <c r="B16" t="n">
-        <v>91417</v>
+        <v>97989</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1588</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789477</v>
+        <v>789136</v>
       </c>
       <c r="R16" t="n">
-        <v>7358460</v>
+        <v>7358773</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2146,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699592</v>
+        <v>125699609</v>
       </c>
       <c r="B17" t="n">
-        <v>57053</v>
+        <v>97989</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2157,21 +2166,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789386</v>
+        <v>789218</v>
       </c>
       <c r="R17" t="n">
-        <v>7358462</v>
+        <v>7358692</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2217,11 +2226,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2248,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699593</v>
+        <v>125699610</v>
       </c>
       <c r="B18" t="n">
-        <v>57053</v>
+        <v>97989</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2259,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789386</v>
+        <v>789467</v>
       </c>
       <c r="R18" t="n">
-        <v>7358451</v>
+        <v>7358419</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2350,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125699597</v>
+        <v>125699591</v>
       </c>
       <c r="B19" t="n">
-        <v>57816</v>
+        <v>79917</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2361,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2385,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789475</v>
+        <v>789411</v>
       </c>
       <c r="R19" t="n">
-        <v>7358466</v>
+        <v>7358493</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2429,6 +2428,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2444,6 +2444,297 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125699598</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lill Hällforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>789394</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7358477</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125699599</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lill Hällforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>789428</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7358468</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125699601</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lill Hällforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>789452</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7358494</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23044-2025 artfynd.xlsx
+++ b/artfynd/A 23044-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699587</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699588</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699612</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699614</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699615</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699611</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699589</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699590</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1551,6 +1596,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699592</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1653,6 +1703,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699593</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1755,6 +1810,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699594</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1852,6 +1912,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699595</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699596</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699597</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699608</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699609</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699610</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2444,6 +2534,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699591</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2541,6 +2636,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699598</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2638,6 +2738,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699599</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2735,8 +2840,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125699601</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>